--- a/results/02_taxa_assemblage/MRT_Method/ModelD_AllSites/tables/site_eval_train.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelD_AllSites/tables/site_eval_train.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>3.2004</v>
@@ -538,19 +538,19 @@
         <v>0.78</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>3.3528</v>
@@ -591,19 +591,19 @@
         <v>1.43</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -618,15 +618,15 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>6.2484</v>
@@ -644,19 +644,19 @@
         <v>1.57</v>
       </c>
       <c r="J4" t="n">
-        <v>0.125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L4" t="n">
-        <v>0.875</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M4" t="n">
-        <v>0.875</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N4" t="n">
-        <v>0.75</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         <v>0.87</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -750,19 +750,19 @@
         <v>1.795</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -803,19 +803,19 @@
         <v>1.81</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>9.144</v>
@@ -856,19 +856,19 @@
         <v>1.45</v>
       </c>
       <c r="J8" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="M8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -909,19 +909,19 @@
         <v>3.99</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>10.668</v>
@@ -962,19 +962,19 @@
         <v>2.18</v>
       </c>
       <c r="J10" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="M10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>8.077200000000001</v>
@@ -1015,19 +1015,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="J11" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="M11" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1068,19 +1068,19 @@
         <v>0.88</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1095,15 +1095,15 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>1.524</v>
@@ -1121,19 +1121,19 @@
         <v>7.11</v>
       </c>
       <c r="J13" t="n">
-        <v>0.125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L13" t="n">
-        <v>0.875</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M13" t="n">
-        <v>0.875</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N13" t="n">
-        <v>0.75</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1148,15 +1148,15 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>1.3716</v>
@@ -1174,19 +1174,19 @@
         <v>3.61</v>
       </c>
       <c r="J14" t="n">
-        <v>0.125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L14" t="n">
-        <v>0.875</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M14" t="n">
-        <v>0.875</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N14" t="n">
-        <v>0.75</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>6.7056</v>
@@ -1227,19 +1227,19 @@
         <v>2.13</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1280,19 +1280,19 @@
         <v>1.25</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1333,19 +1333,19 @@
         <v>1.12</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L17" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1386,19 +1386,19 @@
         <v>1.53</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L18" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1439,19 +1439,19 @@
         <v>1.1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L19" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1492,19 +1492,19 @@
         <v>2.47</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L20" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1598,19 +1598,19 @@
         <v>1.16</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1625,11 +1625,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1651,19 +1651,19 @@
         <v>1.55</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L23" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1704,19 +1704,19 @@
         <v>1.82</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L24" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1757,19 +1757,19 @@
         <v>1.07</v>
       </c>
       <c r="J25" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1784,15 +1784,15 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>4.6</v>
@@ -1810,19 +1810,19 @@
         <v>0.41342143147169</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1863,19 +1863,19 @@
         <v>1.08693561108866</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L27" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1916,19 +1916,19 @@
         <v>1.50490599353894</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L28" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N28" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1969,19 +1969,19 @@
         <v>1.71138107667851</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L29" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N29" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -2022,19 +2022,19 @@
         <v>0.806961722029484</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2075,19 +2075,19 @@
         <v>2.16766115621638</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L31" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2128,19 +2128,19 @@
         <v>1.05926908510679</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L32" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2181,19 +2181,19 @@
         <v>1.84203344898835</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L33" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N33" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2208,15 +2208,15 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
         <v>0.5</v>
@@ -2234,19 +2234,19 @@
         <v>1.53</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6666666666666667</v>
+        <v>1</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -2287,19 +2287,19 @@
         <v>1.52091254752852</v>
       </c>
       <c r="J35" t="n">
-        <v>0.125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L35" t="n">
-        <v>0.875</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M35" t="n">
-        <v>0.875</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N35" t="n">
-        <v>0.75</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2340,19 +2340,19 @@
         <v>1.21254379102751</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L36" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N36" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0.8</v>
@@ -2393,19 +2393,19 @@
         <v>0.541078316722817</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>2</v>
@@ -2446,19 +2446,19 @@
         <v>0.850441042680259</v>
       </c>
       <c r="J38" t="n">
-        <v>0.125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L38" t="n">
-        <v>0.875</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M38" t="n">
-        <v>0.875</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N38" t="n">
-        <v>0.75</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
         <v>2.2</v>
@@ -2499,19 +2499,19 @@
         <v>2.14788592339205</v>
       </c>
       <c r="J39" t="n">
-        <v>0.125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L39" t="n">
-        <v>0.875</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M39" t="n">
-        <v>0.875</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N39" t="n">
-        <v>0.75</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2552,19 +2552,19 @@
         <v>0.542826236601442</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N40" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2579,15 +2579,15 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>4.3</v>
@@ -2605,19 +2605,19 @@
         <v>0.758892017654233</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N41" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>1.2</v>
@@ -2658,19 +2658,19 @@
         <v>0.511201323109319</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K42" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M42" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N42" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -2685,15 +2685,15 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>4.3</v>
@@ -2711,19 +2711,19 @@
         <v>0.601560297020399</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N43" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -2764,19 +2764,19 @@
         <v>0.67004569366047</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N44" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2817,19 +2817,19 @@
         <v>1.84144213994961</v>
       </c>
       <c r="J45" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -2848,11 +2848,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>4.6</v>
@@ -2870,19 +2870,19 @@
         <v>0.719020334793854</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -2897,15 +2897,15 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>3.4</v>
@@ -2923,19 +2923,19 @@
         <v>1.07155989004254</v>
       </c>
       <c r="J47" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K47" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N47" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -2950,11 +2950,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2976,19 +2976,19 @@
         <v>1.50636152676643</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L48" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N48" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3029,19 +3029,19 @@
         <v>1.16723767030516</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L49" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N49" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3082,19 +3082,19 @@
         <v>1.00433351312142</v>
       </c>
       <c r="J50" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0625</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L50" t="n">
-        <v>0.125</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8125</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N50" t="n">
-        <v>0.6875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -3135,19 +3135,19 @@
         <v>0.942177344013984</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="M51" t="n">
-        <v>0.8</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N51" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>

--- a/results/02_taxa_assemblage/MRT_Method/ModelD_AllSites/tables/site_eval_train.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelD_AllSites/tables/site_eval_train.xlsx
@@ -538,19 +538,19 @@
         <v>0.78</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -591,19 +591,19 @@
         <v>1.43</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -644,19 +644,19 @@
         <v>1.57</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         <v>0.87</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1121,19 +1121,19 @@
         <v>7.11</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K13" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>3.61</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K14" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1227,19 +1227,19 @@
         <v>2.13</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K15" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1333,19 +1333,19 @@
         <v>1.12</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K17" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1386,19 +1386,19 @@
         <v>1.53</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K18" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1439,19 +1439,19 @@
         <v>1.1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K19" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1492,19 +1492,19 @@
         <v>2.47</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K20" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K21" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1651,19 +1651,19 @@
         <v>1.55</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K23" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1704,19 +1704,19 @@
         <v>1.82</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K24" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0.4</v>
@@ -1757,19 +1757,19 @@
         <v>1.07</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1810,19 +1810,19 @@
         <v>0.41342143147169</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K26" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N26" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1863,19 +1863,19 @@
         <v>1.08693561108866</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K27" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N27" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1916,19 +1916,19 @@
         <v>1.50490599353894</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K28" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N28" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1969,19 +1969,19 @@
         <v>1.71138107667851</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K29" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N29" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         <v>0.806961722029484</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K30" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N30" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2075,19 +2075,19 @@
         <v>2.16766115621638</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K31" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N31" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2128,19 +2128,19 @@
         <v>1.05926908510679</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K32" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L32" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N32" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2181,19 +2181,19 @@
         <v>1.84203344898835</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K33" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N33" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2212,11 +2212,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>0.5</v>
@@ -2234,19 +2234,19 @@
         <v>1.53</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2287,19 +2287,19 @@
         <v>1.52091254752852</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K35" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N35" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2340,19 +2340,19 @@
         <v>1.21254379102751</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K36" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L36" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N36" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2393,19 +2393,19 @@
         <v>0.541078316722817</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K37" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N37" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2446,19 +2446,19 @@
         <v>0.850441042680259</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K38" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2499,19 +2499,19 @@
         <v>2.14788592339205</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K39" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N39" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2552,19 +2552,19 @@
         <v>0.542826236601442</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K40" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N40" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2605,19 +2605,19 @@
         <v>0.758892017654233</v>
       </c>
       <c r="J41" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K41" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N41" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2658,19 +2658,19 @@
         <v>0.511201323109319</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K42" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L42" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N42" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -2711,19 +2711,19 @@
         <v>0.601560297020399</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K43" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L43" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M43" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N43" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -2764,19 +2764,19 @@
         <v>0.67004569366047</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K44" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L44" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N44" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -2795,11 +2795,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>1.2</v>
@@ -2817,19 +2817,19 @@
         <v>1.84144213994961</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2870,19 +2870,19 @@
         <v>0.719020334793854</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K46" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L46" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N46" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2923,19 +2923,19 @@
         <v>1.07155989004254</v>
       </c>
       <c r="J47" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K47" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L47" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M47" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N47" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2976,19 +2976,19 @@
         <v>1.50636152676643</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K48" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L48" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M48" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N48" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3029,19 +3029,19 @@
         <v>1.16723767030516</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K49" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L49" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M49" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N49" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3082,19 +3082,19 @@
         <v>1.00433351312142</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K50" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L50" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M50" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N50" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3135,19 +3135,19 @@
         <v>0.942177344013984</v>
       </c>
       <c r="J51" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K51" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="L51" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="M51" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="N51" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.4634146341463414</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
